--- a/templates/import_template.xlsx
+++ b/templates/import_template.xlsx
@@ -19,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,30 +31,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="00A62A36"/>
-      <sz val="14"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <color rgb="001F1B1B"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="001F1B1B"/>
-      <sz val="11"/>
+      <color rgb="008E232E"/>
+      <sz val="12"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <color rgb="008E232E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <i val="1"/>
-      <color rgb="00888888"/>
+      <color rgb="008A7E7C"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -66,7 +85,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FBEEEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008E232E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAF7F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E6CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,26 +119,26 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00EADDDB"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00EADDDB"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00EADDDB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00EADDDB"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -107,10 +146,60 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -476,99 +565,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>統一證券 / Justinvestment — 資料匯入範本</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>請依下列分頁填寫，灰色斜體列為「範例」，匯入前請刪除範例列。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>【客戶】= 投資人 (你服務的客戶)。必填：姓名。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>【商品】= 結構型商品 (SN/ELN/PGN…)。必填：商品代號。SN 類才需填 KO/KI/票息/標的。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>【投資】= 把投資人連到商品 (持倉)。必填：客戶姓名、商品代號、投資金額。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>格式規定：</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>• 日期：YYYY-MM-DD (例 2026-06-18)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>• 百分比欄 (KO/KI/履約/票息)：填數字即可，例 KO=100、KI=60、票息=8 (代表 8% 年化)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>• 金額：純數字，不要逗號或貨幣符號</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>• 配息頻率：月配 / 季配 / 半年配 / 年配 / 到期一次</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>• 客戶姓名（投資分頁）必須與【客戶】分頁的姓名一字不差，才能正確連結</t>
+          <t xml:space="preserve">  Justinvestment · 資料匯入範本</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1"/>
+    <row r="4" ht="8" customHeight="1">
+      <c r="B4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>填寫方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>只需在各分頁輸入資料即可，版面已排好、無需美化。灰金色斜體列為「範例」，匯入前請刪除。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="8" customHeight="1">
+      <c r="B7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>分頁說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>客戶 — 投資人 (你服務的客戶)。必填：姓名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>商品 — 結構型商品 (SN/ELN/PGN…)。必填：商品代號。SN 類才需填 KO/KI/票息/標的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>投資 — 將投資人連到商品 (持倉)。必填：客戶姓名、商品代號、投資金額。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="8" customHeight="1">
+      <c r="B12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>格式規定</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>日期：YYYY-MM-DD（例 2026-06-18）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>百分比欄（KO/KI/履約/票息）：填數字即可，例 KO=100、KI=60、票息=8（代表 8% 年化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>金額：純數字，勿加逗號或貨幣符號</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>配息頻率：月配 / 季配 / 半年配 / 年配 / 到期一次（可用下拉選）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>「投資」分頁的客戶姓名，需與「客戶」分頁完全一致才能正確連結</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -579,67 +687,498 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>姓名*</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
+          <t xml:space="preserve">  Justinvestment · 客戶 (投資人)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  你服務的投資人名單 · 必填：姓名</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>姓名 *</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>美元額度</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>幣別</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>統一帳號</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>蔣太太</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B4" s="8" t="n">
         <v>370000</v>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr"/>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>範例列，請刪除</t>
-        </is>
-      </c>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>← 範例，請刪除</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="9" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="9" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="11" t="n"/>
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="9" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="11" t="n"/>
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="9" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="11" t="n"/>
+      <c r="B46" s="12" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="9" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="11" t="n"/>
+      <c r="B48" s="12" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="9" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="11" t="n"/>
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="9" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="11" t="n"/>
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="9" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="11" t="n"/>
+      <c r="B54" s="12" t="n"/>
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="9" t="n"/>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="9" t="n"/>
+      <c r="E55" s="9" t="n"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="11" t="n"/>
+      <c r="B56" s="12" t="n"/>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="11" t="n"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="9" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="11" t="n"/>
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="11" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="n"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="11" t="n"/>
+      <c r="B60" s="12" t="n"/>
+      <c r="C60" s="11" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="11" t="n"/>
+      <c r="B62" s="12" t="n"/>
+      <c r="C62" s="11" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="9" t="n"/>
+      <c r="D63" s="9" t="n"/>
+      <c r="E63" s="9" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C4:C63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"USD,TWD,HKD,EUR,JPY,CNY"</formula1>
     </dataValidation>
   </dataValidations>
@@ -653,193 +1192,1336 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>商品代號*</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
+          <t xml:space="preserve">  Justinvestment · 商品 (結構型商品)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SN/ELN/PGN 等 · 必填：商品代號 · % 欄填數字 (KO=100…)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>商品代號 *</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>類別</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>標的1</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>期初價1</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>標的2</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>期初價2</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>標的3</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>期初價3</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>KO障壁(%)</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>KI障壁(%)</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>履約價(%)</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>票息(%年化)</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>KO障壁
+(%)</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>KI障壁
+(%)</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>履約價
+(%)</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>票息
+(%年化)</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>配息頻率</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>成交日</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>比價日</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>到期日</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>狀態</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>EQDS0702653</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D4" s="13" t="n">
         <v>250.5</v>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>TSM</t>
         </is>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F4" s="13" t="n">
         <v>180.2</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>ANET</t>
         </is>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H4" s="13" t="n">
         <v>95</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I4" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J4" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="K4" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="L4" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>月配</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N4" s="15" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O4" s="15" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="P4" s="15" t="inlineStr"/>
+      <c r="Q4" s="7" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
     </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="17" t="n"/>
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="17" t="n"/>
+      <c r="L5" s="17" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="18" t="n"/>
+      <c r="O5" s="18" t="n"/>
+      <c r="P5" s="18" t="n"/>
+      <c r="Q5" s="9" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="19" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="19" t="n"/>
+      <c r="I6" s="20" t="n"/>
+      <c r="J6" s="20" t="n"/>
+      <c r="K6" s="20" t="n"/>
+      <c r="L6" s="20" t="n"/>
+      <c r="M6" s="11" t="n"/>
+      <c r="N6" s="21" t="n"/>
+      <c r="O6" s="21" t="n"/>
+      <c r="P6" s="21" t="n"/>
+      <c r="Q6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="18" t="n"/>
+      <c r="O7" s="18" t="n"/>
+      <c r="P7" s="18" t="n"/>
+      <c r="Q7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="19" t="n"/>
+      <c r="I8" s="20" t="n"/>
+      <c r="J8" s="20" t="n"/>
+      <c r="K8" s="20" t="n"/>
+      <c r="L8" s="20" t="n"/>
+      <c r="M8" s="11" t="n"/>
+      <c r="N8" s="21" t="n"/>
+      <c r="O8" s="21" t="n"/>
+      <c r="P8" s="21" t="n"/>
+      <c r="Q8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="17" t="n"/>
+      <c r="J9" s="17" t="n"/>
+      <c r="K9" s="17" t="n"/>
+      <c r="L9" s="17" t="n"/>
+      <c r="M9" s="9" t="n"/>
+      <c r="N9" s="18" t="n"/>
+      <c r="O9" s="18" t="n"/>
+      <c r="P9" s="18" t="n"/>
+      <c r="Q9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="20" t="n"/>
+      <c r="J10" s="20" t="n"/>
+      <c r="K10" s="20" t="n"/>
+      <c r="L10" s="20" t="n"/>
+      <c r="M10" s="11" t="n"/>
+      <c r="N10" s="21" t="n"/>
+      <c r="O10" s="21" t="n"/>
+      <c r="P10" s="21" t="n"/>
+      <c r="Q10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="17" t="n"/>
+      <c r="J11" s="17" t="n"/>
+      <c r="K11" s="17" t="n"/>
+      <c r="L11" s="17" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="18" t="n"/>
+      <c r="O11" s="18" t="n"/>
+      <c r="P11" s="18" t="n"/>
+      <c r="Q11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="20" t="n"/>
+      <c r="K12" s="20" t="n"/>
+      <c r="L12" s="20" t="n"/>
+      <c r="M12" s="11" t="n"/>
+      <c r="N12" s="21" t="n"/>
+      <c r="O12" s="21" t="n"/>
+      <c r="P12" s="21" t="n"/>
+      <c r="Q12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="16" t="n"/>
+      <c r="I13" s="17" t="n"/>
+      <c r="J13" s="17" t="n"/>
+      <c r="K13" s="17" t="n"/>
+      <c r="L13" s="17" t="n"/>
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="18" t="n"/>
+      <c r="O13" s="18" t="n"/>
+      <c r="P13" s="18" t="n"/>
+      <c r="Q13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="20" t="n"/>
+      <c r="J14" s="20" t="n"/>
+      <c r="K14" s="20" t="n"/>
+      <c r="L14" s="20" t="n"/>
+      <c r="M14" s="11" t="n"/>
+      <c r="N14" s="21" t="n"/>
+      <c r="O14" s="21" t="n"/>
+      <c r="P14" s="21" t="n"/>
+      <c r="Q14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="16" t="n"/>
+      <c r="I15" s="17" t="n"/>
+      <c r="J15" s="17" t="n"/>
+      <c r="K15" s="17" t="n"/>
+      <c r="L15" s="17" t="n"/>
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="18" t="n"/>
+      <c r="O15" s="18" t="n"/>
+      <c r="P15" s="18" t="n"/>
+      <c r="Q15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="20" t="n"/>
+      <c r="J16" s="20" t="n"/>
+      <c r="K16" s="20" t="n"/>
+      <c r="L16" s="20" t="n"/>
+      <c r="M16" s="11" t="n"/>
+      <c r="N16" s="21" t="n"/>
+      <c r="O16" s="21" t="n"/>
+      <c r="P16" s="21" t="n"/>
+      <c r="Q16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="17" t="n"/>
+      <c r="J17" s="17" t="n"/>
+      <c r="K17" s="17" t="n"/>
+      <c r="L17" s="17" t="n"/>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="18" t="n"/>
+      <c r="O17" s="18" t="n"/>
+      <c r="P17" s="18" t="n"/>
+      <c r="Q17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="20" t="n"/>
+      <c r="J18" s="20" t="n"/>
+      <c r="K18" s="20" t="n"/>
+      <c r="L18" s="20" t="n"/>
+      <c r="M18" s="11" t="n"/>
+      <c r="N18" s="21" t="n"/>
+      <c r="O18" s="21" t="n"/>
+      <c r="P18" s="21" t="n"/>
+      <c r="Q18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="16" t="n"/>
+      <c r="I19" s="17" t="n"/>
+      <c r="J19" s="17" t="n"/>
+      <c r="K19" s="17" t="n"/>
+      <c r="L19" s="17" t="n"/>
+      <c r="M19" s="9" t="n"/>
+      <c r="N19" s="18" t="n"/>
+      <c r="O19" s="18" t="n"/>
+      <c r="P19" s="18" t="n"/>
+      <c r="Q19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="20" t="n"/>
+      <c r="J20" s="20" t="n"/>
+      <c r="K20" s="20" t="n"/>
+      <c r="L20" s="20" t="n"/>
+      <c r="M20" s="11" t="n"/>
+      <c r="N20" s="21" t="n"/>
+      <c r="O20" s="21" t="n"/>
+      <c r="P20" s="21" t="n"/>
+      <c r="Q20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="16" t="n"/>
+      <c r="I21" s="17" t="n"/>
+      <c r="J21" s="17" t="n"/>
+      <c r="K21" s="17" t="n"/>
+      <c r="L21" s="17" t="n"/>
+      <c r="M21" s="9" t="n"/>
+      <c r="N21" s="18" t="n"/>
+      <c r="O21" s="18" t="n"/>
+      <c r="P21" s="18" t="n"/>
+      <c r="Q21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="20" t="n"/>
+      <c r="J22" s="20" t="n"/>
+      <c r="K22" s="20" t="n"/>
+      <c r="L22" s="20" t="n"/>
+      <c r="M22" s="11" t="n"/>
+      <c r="N22" s="21" t="n"/>
+      <c r="O22" s="21" t="n"/>
+      <c r="P22" s="21" t="n"/>
+      <c r="Q22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="16" t="n"/>
+      <c r="I23" s="17" t="n"/>
+      <c r="J23" s="17" t="n"/>
+      <c r="K23" s="17" t="n"/>
+      <c r="L23" s="17" t="n"/>
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="18" t="n"/>
+      <c r="O23" s="18" t="n"/>
+      <c r="P23" s="18" t="n"/>
+      <c r="Q23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="19" t="n"/>
+      <c r="I24" s="20" t="n"/>
+      <c r="J24" s="20" t="n"/>
+      <c r="K24" s="20" t="n"/>
+      <c r="L24" s="20" t="n"/>
+      <c r="M24" s="11" t="n"/>
+      <c r="N24" s="21" t="n"/>
+      <c r="O24" s="21" t="n"/>
+      <c r="P24" s="21" t="n"/>
+      <c r="Q24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="17" t="n"/>
+      <c r="J25" s="17" t="n"/>
+      <c r="K25" s="17" t="n"/>
+      <c r="L25" s="17" t="n"/>
+      <c r="M25" s="9" t="n"/>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="18" t="n"/>
+      <c r="P25" s="18" t="n"/>
+      <c r="Q25" s="9" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="19" t="n"/>
+      <c r="I26" s="20" t="n"/>
+      <c r="J26" s="20" t="n"/>
+      <c r="K26" s="20" t="n"/>
+      <c r="L26" s="20" t="n"/>
+      <c r="M26" s="11" t="n"/>
+      <c r="N26" s="21" t="n"/>
+      <c r="O26" s="21" t="n"/>
+      <c r="P26" s="21" t="n"/>
+      <c r="Q26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="16" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="16" t="n"/>
+      <c r="I27" s="17" t="n"/>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="17" t="n"/>
+      <c r="L27" s="17" t="n"/>
+      <c r="M27" s="9" t="n"/>
+      <c r="N27" s="18" t="n"/>
+      <c r="O27" s="18" t="n"/>
+      <c r="P27" s="18" t="n"/>
+      <c r="Q27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="19" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="19" t="n"/>
+      <c r="I28" s="20" t="n"/>
+      <c r="J28" s="20" t="n"/>
+      <c r="K28" s="20" t="n"/>
+      <c r="L28" s="20" t="n"/>
+      <c r="M28" s="11" t="n"/>
+      <c r="N28" s="21" t="n"/>
+      <c r="O28" s="21" t="n"/>
+      <c r="P28" s="21" t="n"/>
+      <c r="Q28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="16" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
+      <c r="L29" s="17" t="n"/>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="18" t="n"/>
+      <c r="O29" s="18" t="n"/>
+      <c r="P29" s="18" t="n"/>
+      <c r="Q29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="19" t="n"/>
+      <c r="I30" s="20" t="n"/>
+      <c r="J30" s="20" t="n"/>
+      <c r="K30" s="20" t="n"/>
+      <c r="L30" s="20" t="n"/>
+      <c r="M30" s="11" t="n"/>
+      <c r="N30" s="21" t="n"/>
+      <c r="O30" s="21" t="n"/>
+      <c r="P30" s="21" t="n"/>
+      <c r="Q30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="16" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="16" t="n"/>
+      <c r="I31" s="17" t="n"/>
+      <c r="J31" s="17" t="n"/>
+      <c r="K31" s="17" t="n"/>
+      <c r="L31" s="17" t="n"/>
+      <c r="M31" s="9" t="n"/>
+      <c r="N31" s="18" t="n"/>
+      <c r="O31" s="18" t="n"/>
+      <c r="P31" s="18" t="n"/>
+      <c r="Q31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="19" t="n"/>
+      <c r="I32" s="20" t="n"/>
+      <c r="J32" s="20" t="n"/>
+      <c r="K32" s="20" t="n"/>
+      <c r="L32" s="20" t="n"/>
+      <c r="M32" s="11" t="n"/>
+      <c r="N32" s="21" t="n"/>
+      <c r="O32" s="21" t="n"/>
+      <c r="P32" s="21" t="n"/>
+      <c r="Q32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="9" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="16" t="n"/>
+      <c r="I33" s="17" t="n"/>
+      <c r="J33" s="17" t="n"/>
+      <c r="K33" s="17" t="n"/>
+      <c r="L33" s="17" t="n"/>
+      <c r="M33" s="9" t="n"/>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="18" t="n"/>
+      <c r="P33" s="18" t="n"/>
+      <c r="Q33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="19" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="19" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="19" t="n"/>
+      <c r="I34" s="20" t="n"/>
+      <c r="J34" s="20" t="n"/>
+      <c r="K34" s="20" t="n"/>
+      <c r="L34" s="20" t="n"/>
+      <c r="M34" s="11" t="n"/>
+      <c r="N34" s="21" t="n"/>
+      <c r="O34" s="21" t="n"/>
+      <c r="P34" s="21" t="n"/>
+      <c r="Q34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="9" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="16" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="16" t="n"/>
+      <c r="I35" s="17" t="n"/>
+      <c r="J35" s="17" t="n"/>
+      <c r="K35" s="17" t="n"/>
+      <c r="L35" s="17" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="18" t="n"/>
+      <c r="O35" s="18" t="n"/>
+      <c r="P35" s="18" t="n"/>
+      <c r="Q35" s="9" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="19" t="n"/>
+      <c r="I36" s="20" t="n"/>
+      <c r="J36" s="20" t="n"/>
+      <c r="K36" s="20" t="n"/>
+      <c r="L36" s="20" t="n"/>
+      <c r="M36" s="11" t="n"/>
+      <c r="N36" s="21" t="n"/>
+      <c r="O36" s="21" t="n"/>
+      <c r="P36" s="21" t="n"/>
+      <c r="Q36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="16" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="17" t="n"/>
+      <c r="L37" s="17" t="n"/>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="18" t="n"/>
+      <c r="O37" s="18" t="n"/>
+      <c r="P37" s="18" t="n"/>
+      <c r="Q37" s="9" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="11" t="n"/>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="19" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="19" t="n"/>
+      <c r="I38" s="20" t="n"/>
+      <c r="J38" s="20" t="n"/>
+      <c r="K38" s="20" t="n"/>
+      <c r="L38" s="20" t="n"/>
+      <c r="M38" s="11" t="n"/>
+      <c r="N38" s="21" t="n"/>
+      <c r="O38" s="21" t="n"/>
+      <c r="P38" s="21" t="n"/>
+      <c r="Q38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="9" t="n"/>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="16" t="n"/>
+      <c r="I39" s="17" t="n"/>
+      <c r="J39" s="17" t="n"/>
+      <c r="K39" s="17" t="n"/>
+      <c r="L39" s="17" t="n"/>
+      <c r="M39" s="9" t="n"/>
+      <c r="N39" s="18" t="n"/>
+      <c r="O39" s="18" t="n"/>
+      <c r="P39" s="18" t="n"/>
+      <c r="Q39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="11" t="n"/>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="19" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="19" t="n"/>
+      <c r="I40" s="20" t="n"/>
+      <c r="J40" s="20" t="n"/>
+      <c r="K40" s="20" t="n"/>
+      <c r="L40" s="20" t="n"/>
+      <c r="M40" s="11" t="n"/>
+      <c r="N40" s="21" t="n"/>
+      <c r="O40" s="21" t="n"/>
+      <c r="P40" s="21" t="n"/>
+      <c r="Q40" s="11" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="9" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="16" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="16" t="n"/>
+      <c r="I41" s="17" t="n"/>
+      <c r="J41" s="17" t="n"/>
+      <c r="K41" s="17" t="n"/>
+      <c r="L41" s="17" t="n"/>
+      <c r="M41" s="9" t="n"/>
+      <c r="N41" s="18" t="n"/>
+      <c r="O41" s="18" t="n"/>
+      <c r="P41" s="18" t="n"/>
+      <c r="Q41" s="9" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="19" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="19" t="n"/>
+      <c r="I42" s="20" t="n"/>
+      <c r="J42" s="20" t="n"/>
+      <c r="K42" s="20" t="n"/>
+      <c r="L42" s="20" t="n"/>
+      <c r="M42" s="11" t="n"/>
+      <c r="N42" s="21" t="n"/>
+      <c r="O42" s="21" t="n"/>
+      <c r="P42" s="21" t="n"/>
+      <c r="Q42" s="11" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="16" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="16" t="n"/>
+      <c r="I43" s="17" t="n"/>
+      <c r="J43" s="17" t="n"/>
+      <c r="K43" s="17" t="n"/>
+      <c r="L43" s="17" t="n"/>
+      <c r="M43" s="9" t="n"/>
+      <c r="N43" s="18" t="n"/>
+      <c r="O43" s="18" t="n"/>
+      <c r="P43" s="18" t="n"/>
+      <c r="Q43" s="9" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="19" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="19" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="19" t="n"/>
+      <c r="I44" s="20" t="n"/>
+      <c r="J44" s="20" t="n"/>
+      <c r="K44" s="20" t="n"/>
+      <c r="L44" s="20" t="n"/>
+      <c r="M44" s="11" t="n"/>
+      <c r="N44" s="21" t="n"/>
+      <c r="O44" s="21" t="n"/>
+      <c r="P44" s="21" t="n"/>
+      <c r="Q44" s="11" t="n"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="16" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="16" t="n"/>
+      <c r="I45" s="17" t="n"/>
+      <c r="J45" s="17" t="n"/>
+      <c r="K45" s="17" t="n"/>
+      <c r="L45" s="17" t="n"/>
+      <c r="M45" s="9" t="n"/>
+      <c r="N45" s="18" t="n"/>
+      <c r="O45" s="18" t="n"/>
+      <c r="P45" s="18" t="n"/>
+      <c r="Q45" s="9" t="n"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="11" t="n"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="19" t="n"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="19" t="n"/>
+      <c r="I46" s="20" t="n"/>
+      <c r="J46" s="20" t="n"/>
+      <c r="K46" s="20" t="n"/>
+      <c r="L46" s="20" t="n"/>
+      <c r="M46" s="11" t="n"/>
+      <c r="N46" s="21" t="n"/>
+      <c r="O46" s="21" t="n"/>
+      <c r="P46" s="21" t="n"/>
+      <c r="Q46" s="11" t="n"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="9" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="16" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="16" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="16" t="n"/>
+      <c r="I47" s="17" t="n"/>
+      <c r="J47" s="17" t="n"/>
+      <c r="K47" s="17" t="n"/>
+      <c r="L47" s="17" t="n"/>
+      <c r="M47" s="9" t="n"/>
+      <c r="N47" s="18" t="n"/>
+      <c r="O47" s="18" t="n"/>
+      <c r="P47" s="18" t="n"/>
+      <c r="Q47" s="9" t="n"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="11" t="n"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="19" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="19" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="19" t="n"/>
+      <c r="I48" s="20" t="n"/>
+      <c r="J48" s="20" t="n"/>
+      <c r="K48" s="20" t="n"/>
+      <c r="L48" s="20" t="n"/>
+      <c r="M48" s="11" t="n"/>
+      <c r="N48" s="21" t="n"/>
+      <c r="O48" s="21" t="n"/>
+      <c r="P48" s="21" t="n"/>
+      <c r="Q48" s="11" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="9" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="16" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="16" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="16" t="n"/>
+      <c r="I49" s="17" t="n"/>
+      <c r="J49" s="17" t="n"/>
+      <c r="K49" s="17" t="n"/>
+      <c r="L49" s="17" t="n"/>
+      <c r="M49" s="9" t="n"/>
+      <c r="N49" s="18" t="n"/>
+      <c r="O49" s="18" t="n"/>
+      <c r="P49" s="18" t="n"/>
+      <c r="Q49" s="9" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="11" t="n"/>
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="19" t="n"/>
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="19" t="n"/>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="19" t="n"/>
+      <c r="I50" s="20" t="n"/>
+      <c r="J50" s="20" t="n"/>
+      <c r="K50" s="20" t="n"/>
+      <c r="L50" s="20" t="n"/>
+      <c r="M50" s="11" t="n"/>
+      <c r="N50" s="21" t="n"/>
+      <c r="O50" s="21" t="n"/>
+      <c r="P50" s="21" t="n"/>
+      <c r="Q50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="9" t="n"/>
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="16" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="16" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="16" t="n"/>
+      <c r="I51" s="17" t="n"/>
+      <c r="J51" s="17" t="n"/>
+      <c r="K51" s="17" t="n"/>
+      <c r="L51" s="17" t="n"/>
+      <c r="M51" s="9" t="n"/>
+      <c r="N51" s="18" t="n"/>
+      <c r="O51" s="18" t="n"/>
+      <c r="P51" s="18" t="n"/>
+      <c r="Q51" s="9" t="n"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="11" t="n"/>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="19" t="n"/>
+      <c r="E52" s="11" t="n"/>
+      <c r="F52" s="19" t="n"/>
+      <c r="G52" s="11" t="n"/>
+      <c r="H52" s="19" t="n"/>
+      <c r="I52" s="20" t="n"/>
+      <c r="J52" s="20" t="n"/>
+      <c r="K52" s="20" t="n"/>
+      <c r="L52" s="20" t="n"/>
+      <c r="M52" s="11" t="n"/>
+      <c r="N52" s="21" t="n"/>
+      <c r="O52" s="21" t="n"/>
+      <c r="P52" s="21" t="n"/>
+      <c r="Q52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="9" t="n"/>
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="16" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="16" t="n"/>
+      <c r="G53" s="9" t="n"/>
+      <c r="H53" s="16" t="n"/>
+      <c r="I53" s="17" t="n"/>
+      <c r="J53" s="17" t="n"/>
+      <c r="K53" s="17" t="n"/>
+      <c r="L53" s="17" t="n"/>
+      <c r="M53" s="9" t="n"/>
+      <c r="N53" s="18" t="n"/>
+      <c r="O53" s="18" t="n"/>
+      <c r="P53" s="18" t="n"/>
+      <c r="Q53" s="9" t="n"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="11" t="n"/>
+      <c r="B54" s="11" t="n"/>
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="19" t="n"/>
+      <c r="G54" s="11" t="n"/>
+      <c r="H54" s="19" t="n"/>
+      <c r="I54" s="20" t="n"/>
+      <c r="J54" s="20" t="n"/>
+      <c r="K54" s="20" t="n"/>
+      <c r="L54" s="20" t="n"/>
+      <c r="M54" s="11" t="n"/>
+      <c r="N54" s="21" t="n"/>
+      <c r="O54" s="21" t="n"/>
+      <c r="P54" s="21" t="n"/>
+      <c r="Q54" s="11" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="9" t="n"/>
+      <c r="B55" s="9" t="n"/>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="16" t="n"/>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="16" t="n"/>
+      <c r="G55" s="9" t="n"/>
+      <c r="H55" s="16" t="n"/>
+      <c r="I55" s="17" t="n"/>
+      <c r="J55" s="17" t="n"/>
+      <c r="K55" s="17" t="n"/>
+      <c r="L55" s="17" t="n"/>
+      <c r="M55" s="9" t="n"/>
+      <c r="N55" s="18" t="n"/>
+      <c r="O55" s="18" t="n"/>
+      <c r="P55" s="18" t="n"/>
+      <c r="Q55" s="9" t="n"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="11" t="n"/>
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="11" t="n"/>
+      <c r="F56" s="19" t="n"/>
+      <c r="G56" s="11" t="n"/>
+      <c r="H56" s="19" t="n"/>
+      <c r="I56" s="20" t="n"/>
+      <c r="J56" s="20" t="n"/>
+      <c r="K56" s="20" t="n"/>
+      <c r="L56" s="20" t="n"/>
+      <c r="M56" s="11" t="n"/>
+      <c r="N56" s="21" t="n"/>
+      <c r="O56" s="21" t="n"/>
+      <c r="P56" s="21" t="n"/>
+      <c r="Q56" s="11" t="n"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="9" t="n"/>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="16" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="16" t="n"/>
+      <c r="G57" s="9" t="n"/>
+      <c r="H57" s="16" t="n"/>
+      <c r="I57" s="17" t="n"/>
+      <c r="J57" s="17" t="n"/>
+      <c r="K57" s="17" t="n"/>
+      <c r="L57" s="17" t="n"/>
+      <c r="M57" s="9" t="n"/>
+      <c r="N57" s="18" t="n"/>
+      <c r="O57" s="18" t="n"/>
+      <c r="P57" s="18" t="n"/>
+      <c r="Q57" s="9" t="n"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="11" t="n"/>
+      <c r="B58" s="11" t="n"/>
+      <c r="C58" s="11" t="n"/>
+      <c r="D58" s="19" t="n"/>
+      <c r="E58" s="11" t="n"/>
+      <c r="F58" s="19" t="n"/>
+      <c r="G58" s="11" t="n"/>
+      <c r="H58" s="19" t="n"/>
+      <c r="I58" s="20" t="n"/>
+      <c r="J58" s="20" t="n"/>
+      <c r="K58" s="20" t="n"/>
+      <c r="L58" s="20" t="n"/>
+      <c r="M58" s="11" t="n"/>
+      <c r="N58" s="21" t="n"/>
+      <c r="O58" s="21" t="n"/>
+      <c r="P58" s="21" t="n"/>
+      <c r="Q58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="16" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="16" t="n"/>
+      <c r="G59" s="9" t="n"/>
+      <c r="H59" s="16" t="n"/>
+      <c r="I59" s="17" t="n"/>
+      <c r="J59" s="17" t="n"/>
+      <c r="K59" s="17" t="n"/>
+      <c r="L59" s="17" t="n"/>
+      <c r="M59" s="9" t="n"/>
+      <c r="N59" s="18" t="n"/>
+      <c r="O59" s="18" t="n"/>
+      <c r="P59" s="18" t="n"/>
+      <c r="Q59" s="9" t="n"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="11" t="n"/>
+      <c r="B60" s="11" t="n"/>
+      <c r="C60" s="11" t="n"/>
+      <c r="D60" s="19" t="n"/>
+      <c r="E60" s="11" t="n"/>
+      <c r="F60" s="19" t="n"/>
+      <c r="G60" s="11" t="n"/>
+      <c r="H60" s="19" t="n"/>
+      <c r="I60" s="20" t="n"/>
+      <c r="J60" s="20" t="n"/>
+      <c r="K60" s="20" t="n"/>
+      <c r="L60" s="20" t="n"/>
+      <c r="M60" s="11" t="n"/>
+      <c r="N60" s="21" t="n"/>
+      <c r="O60" s="21" t="n"/>
+      <c r="P60" s="21" t="n"/>
+      <c r="Q60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="16" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="16" t="n"/>
+      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="16" t="n"/>
+      <c r="I61" s="17" t="n"/>
+      <c r="J61" s="17" t="n"/>
+      <c r="K61" s="17" t="n"/>
+      <c r="L61" s="17" t="n"/>
+      <c r="M61" s="9" t="n"/>
+      <c r="N61" s="18" t="n"/>
+      <c r="O61" s="18" t="n"/>
+      <c r="P61" s="18" t="n"/>
+      <c r="Q61" s="9" t="n"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="11" t="n"/>
+      <c r="B62" s="11" t="n"/>
+      <c r="C62" s="11" t="n"/>
+      <c r="D62" s="19" t="n"/>
+      <c r="E62" s="11" t="n"/>
+      <c r="F62" s="19" t="n"/>
+      <c r="G62" s="11" t="n"/>
+      <c r="H62" s="19" t="n"/>
+      <c r="I62" s="20" t="n"/>
+      <c r="J62" s="20" t="n"/>
+      <c r="K62" s="20" t="n"/>
+      <c r="L62" s="20" t="n"/>
+      <c r="M62" s="11" t="n"/>
+      <c r="N62" s="21" t="n"/>
+      <c r="O62" s="21" t="n"/>
+      <c r="P62" s="21" t="n"/>
+      <c r="Q62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="9" t="n"/>
+      <c r="C63" s="9" t="n"/>
+      <c r="D63" s="16" t="n"/>
+      <c r="E63" s="9" t="n"/>
+      <c r="F63" s="16" t="n"/>
+      <c r="G63" s="9" t="n"/>
+      <c r="H63" s="16" t="n"/>
+      <c r="I63" s="17" t="n"/>
+      <c r="J63" s="17" t="n"/>
+      <c r="K63" s="17" t="n"/>
+      <c r="L63" s="17" t="n"/>
+      <c r="M63" s="9" t="n"/>
+      <c r="N63" s="18" t="n"/>
+      <c r="O63" s="18" t="n"/>
+      <c r="P63" s="18" t="n"/>
+      <c r="Q63" s="9" t="n"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
+  </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="B2:B200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B4:B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SN,台股,期貨,美股,港股,國內外基金,ELN,PGN,儲蓄險,旅平險,車險,意外險"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M4:M63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"月配,季配,半年配,年配,到期一次"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q4:Q63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"進行中,已出場,暫停"</formula1>
     </dataValidation>
   </dataValidations>
@@ -853,60 +2535,432 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>客戶姓名*</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>商品代號*</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>投資金額*</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
+          <t xml:space="preserve">  Justinvestment · 投資 (持倉)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  把投資人連到商品 · 三欄皆必填 · 客戶姓名須與「客戶」分頁一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>客戶姓名 *</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>商品代號 *</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>投資金額 *</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>幣別</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>蔣太太</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>EQDS0702653</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C4" s="8" t="n">
         <v>370000</v>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
     </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="9" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="9" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="9" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="9" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="9" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="9" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="11" t="n"/>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="9" t="n"/>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="11" t="n"/>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="11" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="9" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="9" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="11" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="9" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="12" t="n"/>
+      <c r="D44" s="11" t="n"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="9" t="n"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="11" t="n"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="12" t="n"/>
+      <c r="D46" s="11" t="n"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="9" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="9" t="n"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="11" t="n"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="12" t="n"/>
+      <c r="D48" s="11" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="9" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="9" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="11" t="n"/>
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="9" t="n"/>
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="9" t="n"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="11" t="n"/>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="9" t="n"/>
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="9" t="n"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="11" t="n"/>
+      <c r="B54" s="11" t="n"/>
+      <c r="C54" s="12" t="n"/>
+      <c r="D54" s="11" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="9" t="n"/>
+      <c r="B55" s="9" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="9" t="n"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="11" t="n"/>
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="12" t="n"/>
+      <c r="D56" s="11" t="n"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="9" t="n"/>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="9" t="n"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="11" t="n"/>
+      <c r="B58" s="11" t="n"/>
+      <c r="C58" s="12" t="n"/>
+      <c r="D58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="9" t="n"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="11" t="n"/>
+      <c r="B60" s="11" t="n"/>
+      <c r="C60" s="12" t="n"/>
+      <c r="D60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="9" t="n"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="11" t="n"/>
+      <c r="B62" s="11" t="n"/>
+      <c r="C62" s="12" t="n"/>
+      <c r="D62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="9" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="9" t="n"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4:D63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"USD,TWD,HKD,EUR,JPY,CNY"</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates/import_template.xlsx
+++ b/templates/import_template.xlsx
@@ -1178,7 +1178,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:C63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C4:C63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="幣別" prompt="請從下拉選單選擇" type="list">
       <formula1>"USD,TWD,HKD,EUR,JPY,CNY"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2514,14 +2514,42 @@
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="B4:B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="10">
+    <dataValidation sqref="B4:B63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="類別" prompt="請從下拉選單選擇" type="list">
       <formula1>"SN,台股,期貨,美股,港股,國內外基金,ELN,PGN,儲蓄險,旅平險,車險,意外險"</formula1>
     </dataValidation>
-    <dataValidation sqref="M4:M63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="KO障壁 (%)" prompt="填數字即可（例 KO=100、票息=8 代表 8%）" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
+    <dataValidation sqref="J4:J63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="KI障壁 (%)" prompt="填數字即可（例 KO=100、票息=8 代表 8%）" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
+    <dataValidation sqref="K4:K63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="履約價 (%)" prompt="填數字即可（例 KO=100、票息=8 代表 8%）" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
+    <dataValidation sqref="L4:L63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="票息 (%年化)" prompt="填數字即可（例 KO=100、票息=8 代表 8%）" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
+    <dataValidation sqref="M4:M63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="配息頻率" prompt="請從下拉選單選擇" type="list">
       <formula1>"月配,季配,半年配,年配,到期一次"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q4:Q63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N4:N63" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="日期格式不正確" error="請用 YYYY-MM-DD（例 2026-06-18）" promptTitle="成交日" prompt="請輸入日期，格式 YYYY-MM-DD（例 2026-06-18）" type="date" operator="between">
+      <formula1>2000-01-01</formula1>
+      <formula2>2100-12-31</formula2>
+    </dataValidation>
+    <dataValidation sqref="O4:O63" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="日期格式不正確" error="請用 YYYY-MM-DD（例 2026-06-18）" promptTitle="比價日" prompt="請輸入日期，格式 YYYY-MM-DD（例 2026-06-18）" type="date" operator="between">
+      <formula1>2000-01-01</formula1>
+      <formula2>2100-12-31</formula2>
+    </dataValidation>
+    <dataValidation sqref="P4:P63" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="日期格式不正確" error="請用 YYYY-MM-DD（例 2026-06-18）" promptTitle="到期日" prompt="請輸入日期，格式 YYYY-MM-DD（例 2026-06-18）" type="date" operator="between">
+      <formula1>2000-01-01</formula1>
+      <formula2>2100-12-31</formula2>
+    </dataValidation>
+    <dataValidation sqref="Q4:Q63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="狀態" prompt="請從下拉選單選擇" type="list">
       <formula1>"進行中,已出場,暫停"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2960,7 +2988,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D4:D63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4:D63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="幣別" prompt="請從下拉選單選擇" type="list">
       <formula1>"USD,TWD,HKD,EUR,JPY,CNY"</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates/import_template.xlsx
+++ b/templates/import_template.xlsx
@@ -12,7 +12,10 @@
     <sheet name="商品" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="投資" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="InvestorList">'客戶'!$A$4:$A$63</definedName>
+    <definedName name="ProductList">'商品'!$A$4:$A$63</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -38,13 +41,13 @@
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
-      <color rgb="001F1B1B"/>
+      <color rgb="001F2A24"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="008E232E"/>
+      <color rgb="00153A2B"/>
       <sz val="12"/>
     </font>
     <font>
@@ -55,7 +58,7 @@
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
-      <color rgb="008E232E"/>
+      <color rgb="00153A2B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,7 +70,7 @@
     <font>
       <name val="Microsoft JhengHei"/>
       <i val="1"/>
-      <color rgb="008A7E7C"/>
+      <color rgb="006E827A"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -80,17 +83,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A62A36"/>
+        <fgColor rgb="001F4D3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBEEEF"/>
+        <fgColor rgb="00E9F2EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008E232E"/>
+        <fgColor rgb="00153A2B"/>
       </patternFill>
     </fill>
     <fill>
@@ -100,7 +103,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF7F7"/>
+        <fgColor rgb="00F4F9F6"/>
       </patternFill>
     </fill>
     <fill>
@@ -119,16 +122,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00EADDDB"/>
+        <color rgb="00D4E5DA"/>
       </left>
       <right style="thin">
-        <color rgb="00EADDDB"/>
+        <color rgb="00D4E5DA"/>
       </right>
       <top style="thin">
-        <color rgb="00EADDDB"/>
+        <color rgb="00D4E5DA"/>
       </top>
       <bottom style="thin">
-        <color rgb="00EADDDB"/>
+        <color rgb="00D4E5DA"/>
       </bottom>
     </border>
   </borders>
@@ -2514,7 +2517,7 @@
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="10">
+  <dataValidations count="13">
     <dataValidation sqref="B4:B63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="類別" prompt="請從下拉選單選擇" type="list">
       <formula1>"SN,台股,期貨,美股,港股,國內外基金,ELN,PGN,儲蓄險,旅平險,車險,意外險"</formula1>
     </dataValidation>
@@ -2552,6 +2555,15 @@
     <dataValidation sqref="Q4:Q63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="狀態" prompt="請從下拉選單選擇" type="list">
       <formula1>"進行中,已出場,暫停"</formula1>
     </dataValidation>
+    <dataValidation sqref="C4:C63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" prompt="可選常用標的，或自行輸入其他代號" type="list">
+      <formula1>"NVDA,TSLA,TSM,ANET,AMD,INTC,AVGO,MSFT,ORCL,MU,GOOG,GOOGL,CRCL,LITE,COHR,QQQ,SPY,SMH,SOXX,IBB,AAPL,AMZN,META,NFLX"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E4:E63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" prompt="可選常用標的，或自行輸入其他代號" type="list">
+      <formula1>"NVDA,TSLA,TSM,ANET,AMD,INTC,AVGO,MSFT,ORCL,MU,GOOG,GOOGL,CRCL,LITE,COHR,QQQ,SPY,SMH,SOXX,IBB,AAPL,AMZN,META,NFLX"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" prompt="可選常用標的，或自行輸入其他代號" type="list">
+      <formula1>"NVDA,TSLA,TSM,ANET,AMD,INTC,AVGO,MSFT,ORCL,MU,GOOG,GOOGL,CRCL,LITE,COHR,QQQ,SPY,SMH,SOXX,IBB,AAPL,AMZN,META,NFLX"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2987,9 +2999,15 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="3">
     <dataValidation sqref="D4:D63" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="幣別" prompt="請從下拉選單選擇" type="list">
       <formula1>"USD,TWD,HKD,EUR,JPY,CNY"</formula1>
+    </dataValidation>
+    <dataValidation sqref="A4:A63" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="從「客戶」分頁選擇，不必重打" type="list">
+      <formula1>InvestorList</formula1>
+    </dataValidation>
+    <dataValidation sqref="B4:B63" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="從「商品」分頁選擇，不必重打" type="list">
+      <formula1>ProductList</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
